--- a/segundo parcial/PROYECTO G1/Copia de matriz grupo 1_.xlsx
+++ b/segundo parcial/PROYECTO G1/Copia de matriz grupo 1_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26D730D4-642C-48AE-8CAF-4BCBE12D4401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8870BA40-A457-4409-A43E-064EF4E70C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato descripción HU" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>Luces encendidas sin necesidad</t>
   </si>
   <si>
-    <t>Ahorrar energía en el hogar</t>
-  </si>
-  <si>
     <t>Detectar presencia de personas</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>Olvido al apagar las luces</t>
   </si>
   <si>
-    <t>Apagar la luz automáticamente</t>
-  </si>
-  <si>
     <t>Programar apagado automático</t>
   </si>
   <si>
@@ -209,9 +203,6 @@
     <t>Encender la luz manualmente en la oscuridad</t>
   </si>
   <si>
-    <t>Brindar comodidad al usuario</t>
-  </si>
-  <si>
     <t>Encender la luz automáticamente</t>
   </si>
   <si>
@@ -236,9 +227,6 @@
     <t>Falta de control en el consumo eléctrico</t>
   </si>
   <si>
-    <t>Reducir desperdicio de energía</t>
-  </si>
-  <si>
     <t>Controlar el uso de la iluminación</t>
   </si>
   <si>
@@ -263,9 +251,6 @@
     <t>Necesidad de un prototipo sencillo</t>
   </si>
   <si>
-    <t>Demostrar el funcionamiento del sistema</t>
-  </si>
-  <si>
     <t>Armar prototipo con Arduino</t>
   </si>
   <si>
@@ -293,9 +278,6 @@
     <t>Posibles errores en la programación</t>
   </si>
   <si>
-    <t>Evitar fallas en el sistema</t>
-  </si>
-  <si>
     <t>Revisar el código del proyecto</t>
   </si>
   <si>
@@ -320,9 +302,6 @@
     <t>No saber si el sistema sirve en casa</t>
   </si>
   <si>
-    <t>Comprobar su utilidad en espacios comunes</t>
-  </si>
-  <si>
     <t>Probar en un espacio de ejemplo</t>
   </si>
   <si>
@@ -344,9 +323,6 @@
     <t>Falta de explicación del funcionamiento</t>
   </si>
   <si>
-    <t>Presentar el proyecto de forma clara</t>
-  </si>
-  <si>
     <t>Explicar el proceso del sistema</t>
   </si>
   <si>
@@ -366,6 +342,30 @@
   </si>
   <si>
     <t>Presentación del proyecto</t>
+  </si>
+  <si>
+    <t>El programa debera Ahorrar energía en el hogar</t>
+  </si>
+  <si>
+    <t>El programa debera Apagar la luz automáticamente</t>
+  </si>
+  <si>
+    <t>El programa debera Brindar comodidad al usuario</t>
+  </si>
+  <si>
+    <t>El programa debera reducir desperdicio de energía</t>
+  </si>
+  <si>
+    <t>El programa debera Demostrar el funcionamiento del sistema</t>
+  </si>
+  <si>
+    <t>El programa debera Evitar fallas en el sistema</t>
+  </si>
+  <si>
+    <t>El programa debera Comprobar su utilidad en espacios comunes</t>
+  </si>
+  <si>
+    <t>El programa debera Presentar el proyecto de forma clara</t>
   </si>
 </sst>
 </file>
@@ -1345,22 +1345,22 @@
         <v>32</v>
       </c>
       <c r="D6" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="F6" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="G6" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="H6" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="61" t="s">
+      <c r="I6" s="61" t="s">
         <v>37</v>
-      </c>
-      <c r="I6" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="J6" s="62"/>
       <c r="K6" s="61" t="s">
@@ -1370,40 +1370,40 @@
         <v>19</v>
       </c>
       <c r="M6" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="61" t="s">
+      <c r="O6" s="61" t="s">
         <v>40</v>
-      </c>
-      <c r="O6" s="61" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="D7" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="F7" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="H7" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="61" t="s">
+      <c r="I7" s="61" t="s">
         <v>46</v>
-      </c>
-      <c r="H7" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="61" t="s">
-        <v>48</v>
       </c>
       <c r="J7" s="62"/>
       <c r="K7" s="61" t="s">
@@ -1413,13 +1413,13 @@
         <v>19</v>
       </c>
       <c r="M7" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" s="61" t="s">
         <v>49</v>
-      </c>
-      <c r="N7" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="61" t="s">
-        <v>51</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -1435,28 +1435,28 @@
     </row>
     <row r="8" spans="1:26" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="F8" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="H8" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="61" t="s">
-        <v>57</v>
-      </c>
       <c r="I8" s="61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="62"/>
       <c r="K8" s="61" t="s">
@@ -1466,81 +1466,81 @@
         <v>19</v>
       </c>
       <c r="M8" s="61" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N8" s="61" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O8" s="61" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="61" t="s">
-        <v>65</v>
-      </c>
       <c r="H9" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J9" s="62"/>
       <c r="K9" s="61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L9" s="61" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="61" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N9" s="61" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O9" s="61" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="H10" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="61" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="61" t="s">
-        <v>76</v>
       </c>
       <c r="J10" s="62"/>
       <c r="K10" s="61" t="s">
@@ -1550,124 +1550,124 @@
         <v>19</v>
       </c>
       <c r="M10" s="61" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N10" s="61" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="61" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D11" s="61" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="E11" s="61" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F11" s="61" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G11" s="61" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H11" s="61" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" s="62"/>
       <c r="K11" s="61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L11" s="61" t="s">
         <v>19</v>
       </c>
       <c r="M11" s="61" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N11" s="61" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O11" s="61" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="61" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E12" s="61" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="61" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H12" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="61" t="s">
         <v>37</v>
-      </c>
-      <c r="I12" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="J12" s="62"/>
       <c r="K12" s="61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L12" s="61" t="s">
         <v>19</v>
       </c>
       <c r="M12" s="61" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="N12" s="61" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="61" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D13" s="61" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E13" s="61" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G13" s="61" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I13" s="61" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J13" s="62"/>
       <c r="K13" s="61" t="s">
@@ -1677,13 +1677,13 @@
         <v>19</v>
       </c>
       <c r="M13" s="61" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="N13" s="61" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7686,7 +7686,7 @@
     <row r="10" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="26"/>
       <c r="C10" s="13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="53" t="str">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D15" s="58" t="str">
         <f>VLOOKUP(C10,'Formato descripción HU'!B6:O14,3,0)</f>
-        <v>Evitar fallas en el sistema</v>
+        <v>El programa debera Evitar fallas en el sistema</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="12"/>
